--- a/research/traditional_assets/database/data/poland/poland_software_internet.xlsx
+++ b/research/traditional_assets/database/data/poland/poland_software_internet.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.2965</v>
+        <v>-0.418</v>
       </c>
       <c r="G2">
-        <v>-2.637770897832818</v>
+        <v>0.04433497536945809</v>
       </c>
       <c r="H2">
-        <v>-2.637770897832818</v>
+        <v>0.04433497536945809</v>
       </c>
       <c r="I2">
-        <v>-2.331269349845201</v>
+        <v>0.04679802955665024</v>
       </c>
       <c r="J2">
-        <v>-2.331269349845201</v>
+        <v>0.04679802955665024</v>
       </c>
       <c r="K2">
-        <v>-0.831</v>
+        <v>0.012</v>
       </c>
       <c r="L2">
-        <v>-2.572755417956656</v>
+        <v>0.02955665024630542</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -615,7 +615,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,73 +624,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.039</v>
+        <v>0.163</v>
       </c>
       <c r="V2">
-        <v>0.006878306878306878</v>
+        <v>0.01523364485981309</v>
       </c>
       <c r="W2">
-        <v>-0.179594598681425</v>
+        <v>-0.0340909090909091</v>
       </c>
       <c r="X2">
-        <v>0.06949797572176278</v>
+        <v>0.1328629998448588</v>
       </c>
       <c r="Y2">
-        <v>-0.2490925744031878</v>
+        <v>-0.1669539089357679</v>
       </c>
       <c r="Z2">
-        <v>0.0898470097357441</v>
+        <v>0.1556151782292066</v>
       </c>
       <c r="AA2">
-        <v>-0.1808806013391707</v>
+        <v>-0.01717791411042945</v>
       </c>
       <c r="AB2">
-        <v>0.06883789759535572</v>
+        <v>0.1321216993065164</v>
       </c>
       <c r="AC2">
-        <v>-0.2497184989345265</v>
+        <v>-0.1492939467233013</v>
       </c>
       <c r="AD2">
-        <v>0.094</v>
+        <v>0.08</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.094</v>
+        <v>0.08</v>
       </c>
       <c r="AG2">
-        <v>0.055</v>
+        <v>-0.083</v>
       </c>
       <c r="AH2">
-        <v>0.01630811936155448</v>
+        <v>0.007421150278293136</v>
       </c>
       <c r="AI2">
-        <v>0.04144620811287478</v>
+        <v>0.01901592583788923</v>
       </c>
       <c r="AJ2">
-        <v>0.009606986899563319</v>
+        <v>-0.007817650937176228</v>
       </c>
       <c r="AK2">
-        <v>0.0246747420367878</v>
+        <v>-0.0205242334322453</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>-0.061</v>
       </c>
       <c r="AN2">
-        <v>-0.1179422835633626</v>
+        <v>-1.454545454545455</v>
+      </c>
+      <c r="AO2">
+        <v>19</v>
       </c>
       <c r="AP2">
-        <v>-0.06900878293601004</v>
+        <v>1.509090909090909</v>
+      </c>
+      <c r="AQ2">
+        <v>-0.3114754098360656</v>
       </c>
     </row>
     <row r="3">
@@ -701,7 +707,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Optizen Labs S.A. (WSE:OPT)</t>
+          <t>Foothills S.A. (WSE:FTL)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -710,25 +716,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.234</v>
-      </c>
-      <c r="G3">
-        <v>0.4493670886075949</v>
-      </c>
-      <c r="H3">
-        <v>0.4493670886075949</v>
-      </c>
-      <c r="I3">
-        <v>0.2848101265822784</v>
-      </c>
-      <c r="J3">
-        <v>0.2848101265822784</v>
+        <v>-0.726</v>
       </c>
       <c r="K3">
-        <v>0.046</v>
-      </c>
-      <c r="L3">
-        <v>0.2911392405063291</v>
+        <v>0.066</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -752,55 +743,46 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.016</v>
+        <v>0.005</v>
       </c>
       <c r="V3">
-        <v>0.003800475059382423</v>
+        <v>0.003246753246753247</v>
       </c>
       <c r="W3">
-        <v>-0.1377245508982036</v>
+        <v>-0.2481203007518797</v>
       </c>
       <c r="X3">
-        <v>0.06942191554722332</v>
+        <v>0.1328629998448588</v>
       </c>
       <c r="Y3">
-        <v>-0.2071464664454269</v>
-      </c>
-      <c r="Z3">
-        <v>-0.548611111111111</v>
-      </c>
-      <c r="AA3">
-        <v>-0.15625</v>
+        <v>-0.3809833005967385</v>
       </c>
       <c r="AB3">
-        <v>0.06882830647450805</v>
-      </c>
-      <c r="AC3">
-        <v>-0.225078306474508</v>
+        <v>0.1321216993065164</v>
       </c>
       <c r="AD3">
-        <v>0.066</v>
+        <v>0.015</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.066</v>
+        <v>0.015</v>
       </c>
       <c r="AG3">
-        <v>0.05</v>
+        <v>0.009999999999999998</v>
       </c>
       <c r="AH3">
-        <v>0.01543498596819458</v>
+        <v>0.009646302250803859</v>
       </c>
       <c r="AI3">
-        <v>-0.33</v>
+        <v>2.142857142857143</v>
       </c>
       <c r="AJ3">
-        <v>0.01173708920187794</v>
+        <v>0.006451612903225806</v>
       </c>
       <c r="AK3">
-        <v>-0.2314814814814815</v>
+        <v>5.000000000000004</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -826,25 +808,25 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.359</v>
+        <v>-0.239</v>
       </c>
       <c r="G4">
-        <v>-5.593939393939394</v>
+        <v>-1.12807881773399</v>
       </c>
       <c r="H4">
-        <v>-5.593939393939394</v>
+        <v>-1.12807881773399</v>
       </c>
       <c r="I4">
-        <v>-4.836363636363636</v>
+        <v>-0.2068965517241379</v>
       </c>
       <c r="J4">
-        <v>-4.836363636363636</v>
+        <v>-0.2068965517241379</v>
       </c>
       <c r="K4">
-        <v>-0.877</v>
+        <v>-0.048</v>
       </c>
       <c r="L4">
-        <v>-5.315151515151515</v>
+        <v>-0.2364532019704433</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -868,67 +850,192 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0.023</v>
+        <v>0.15</v>
       </c>
       <c r="V4">
-        <v>0.01575342465753425</v>
+        <v>0.04854368932038835</v>
       </c>
       <c r="W4">
-        <v>-0.2214646464646465</v>
+        <v>-0.01967213114754099</v>
       </c>
       <c r="X4">
-        <v>0.06957403589630225</v>
+        <v>0.1337168666767719</v>
       </c>
       <c r="Y4">
-        <v>-0.2910386823609487</v>
+        <v>-0.1533889978243129</v>
       </c>
       <c r="Z4">
-        <v>0.0424929178470255</v>
+        <v>0.08302658486707568</v>
       </c>
       <c r="AA4">
-        <v>-0.2055112026783415</v>
+        <v>-0.01717791411042945</v>
       </c>
       <c r="AB4">
-        <v>0.06884748871620337</v>
+        <v>0.1321160326128718</v>
       </c>
       <c r="AC4">
-        <v>-0.2743586913945449</v>
+        <v>-0.1492939467233013</v>
       </c>
       <c r="AD4">
-        <v>0.028</v>
+        <v>0.065</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.028</v>
+        <v>0.065</v>
       </c>
       <c r="AG4">
-        <v>0.005000000000000001</v>
+        <v>-0.08499999999999999</v>
       </c>
       <c r="AH4">
-        <v>0.01881720430107527</v>
+        <v>0.02060221870047544</v>
       </c>
       <c r="AI4">
-        <v>0.0113452188006483</v>
+        <v>0.01599015990159901</v>
       </c>
       <c r="AJ4">
-        <v>0.003412969283276451</v>
+        <v>-0.02828618968386023</v>
       </c>
       <c r="AK4">
-        <v>0.002044989775051125</v>
+        <v>-0.02171136653895274</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>-0.062</v>
       </c>
       <c r="AN4">
-        <v>-0.03513174404015056</v>
+        <v>-1.181818181818182</v>
       </c>
       <c r="AP4">
-        <v>-0.006273525721455459</v>
+        <v>1.545454545454545</v>
+      </c>
+      <c r="AQ4">
+        <v>0.6774193548387097</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Planet B2B S.A. (WSE:P2B)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Software (Internet)</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>-0.418</v>
+      </c>
+      <c r="G5">
+        <v>0.7192118226600984</v>
+      </c>
+      <c r="H5">
+        <v>0.7192118226600984</v>
+      </c>
+      <c r="I5">
+        <v>-0.02463054187192118</v>
+      </c>
+      <c r="J5">
+        <v>-0.02463054187192118</v>
+      </c>
+      <c r="K5">
+        <v>-0.006</v>
+      </c>
+      <c r="L5">
+        <v>-0.02955665024630542</v>
+      </c>
+      <c r="M5">
+        <v>-0</v>
+      </c>
+      <c r="N5">
+        <v>-0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>-0</v>
+      </c>
+      <c r="Q5">
+        <v>-0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0.008</v>
+      </c>
+      <c r="V5">
+        <v>0.001317957166392092</v>
+      </c>
+      <c r="W5">
+        <v>-0.0340909090909091</v>
+      </c>
+      <c r="X5">
+        <v>0.1321266886325951</v>
+      </c>
+      <c r="Y5">
+        <v>-0.1662175977235042</v>
+      </c>
+      <c r="Z5">
+        <v>1.237804878048781</v>
+      </c>
+      <c r="AA5">
+        <v>-0.03048780487804878</v>
+      </c>
+      <c r="AB5">
+        <v>0.1321266886325951</v>
+      </c>
+      <c r="AC5">
+        <v>-0.1626144935106439</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>-0.008</v>
+      </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>-0.001319696469811943</v>
+      </c>
+      <c r="AK5">
+        <v>-0.06299212598425197</v>
+      </c>
+      <c r="AL5">
+        <v>0.001</v>
+      </c>
+      <c r="AM5">
+        <v>0.001</v>
+      </c>
+      <c r="AO5">
+        <v>-5</v>
+      </c>
+      <c r="AQ5">
+        <v>-5</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/poland/poland_software_internet.xlsx
+++ b/research/traditional_assets/database/data/poland/poland_software_internet.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.418</v>
+        <v>-0.455</v>
       </c>
       <c r="G2">
-        <v>0.04433497536945809</v>
+        <v>0.3081232492997199</v>
       </c>
       <c r="H2">
-        <v>0.04433497536945809</v>
+        <v>0.3081232492997199</v>
       </c>
       <c r="I2">
-        <v>0.04679802955665024</v>
+        <v>-0.4173669467787115</v>
       </c>
       <c r="J2">
-        <v>0.04679802955665024</v>
+        <v>-0.4173669467787115</v>
       </c>
       <c r="K2">
-        <v>0.012</v>
+        <v>-0.162</v>
       </c>
       <c r="L2">
-        <v>0.02955665024630542</v>
+        <v>-0.4537815126050421</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -615,7 +615,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,79 +624,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.163</v>
+        <v>0.15</v>
       </c>
       <c r="V2">
-        <v>0.01523364485981309</v>
+        <v>0.01785714285714286</v>
       </c>
       <c r="W2">
-        <v>-0.0340909090909091</v>
+        <v>-0.0265</v>
       </c>
       <c r="X2">
-        <v>0.1328629998448588</v>
+        <v>0.1144093859615791</v>
       </c>
       <c r="Y2">
-        <v>-0.1669539089357679</v>
+        <v>-0.1409093859615791</v>
       </c>
       <c r="Z2">
-        <v>0.1556151782292066</v>
+        <v>0.08827893175074182</v>
       </c>
       <c r="AA2">
-        <v>-0.01717791411042945</v>
+        <v>-0.2047244094488189</v>
       </c>
       <c r="AB2">
-        <v>0.1321216993065164</v>
+        <v>0.1125609879903961</v>
       </c>
       <c r="AC2">
-        <v>-0.1492939467233013</v>
+        <v>-0.3173649981380466</v>
       </c>
       <c r="AD2">
-        <v>0.08</v>
+        <v>0.142</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.08</v>
+        <v>0.142</v>
       </c>
       <c r="AG2">
-        <v>-0.083</v>
+        <v>-0.007999999999999979</v>
       </c>
       <c r="AH2">
-        <v>0.007421150278293136</v>
+        <v>0.01662374151252634</v>
       </c>
       <c r="AI2">
-        <v>0.01901592583788923</v>
+        <v>0.03049173287524157</v>
       </c>
       <c r="AJ2">
-        <v>-0.007817650937176228</v>
+        <v>-0.0009532888465204931</v>
       </c>
       <c r="AK2">
-        <v>-0.0205242334322453</v>
+        <v>-0.001775016640781003</v>
       </c>
       <c r="AL2">
-        <v>0.001</v>
+        <v>0.006</v>
       </c>
       <c r="AM2">
-        <v>-0.061</v>
+        <v>0.003</v>
       </c>
       <c r="AN2">
-        <v>-1.454545454545455</v>
+        <v>-1.775</v>
       </c>
       <c r="AO2">
-        <v>19</v>
+        <v>-24.83333333333333</v>
       </c>
       <c r="AP2">
-        <v>1.509090909090909</v>
+        <v>0.09999999999999974</v>
       </c>
       <c r="AQ2">
-        <v>-0.3114754098360656</v>
+        <v>-49.66666666666666</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +707,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Foothills S.A. (WSE:FTL)</t>
+          <t>BTC Studios S.A. (WSE:BTC)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -716,10 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.726</v>
+        <v>-0.225</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>-0.9595959595959596</v>
+      </c>
+      <c r="J3">
+        <v>-0.9595959595959596</v>
       </c>
       <c r="K3">
-        <v>0.066</v>
+        <v>-0.106</v>
+      </c>
+      <c r="L3">
+        <v>-1.070707070707071</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -728,7 +743,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -737,58 +752,76 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.005</v>
+        <v>0.076</v>
       </c>
       <c r="V3">
-        <v>0.003246753246753247</v>
+        <v>0.02317073170731707</v>
       </c>
       <c r="W3">
-        <v>-0.2481203007518797</v>
+        <v>-0.0265</v>
       </c>
       <c r="X3">
-        <v>0.1328629998448588</v>
+        <v>0.1144093859615791</v>
       </c>
       <c r="Y3">
-        <v>-0.3809833005967385</v>
+        <v>-0.1409093859615791</v>
+      </c>
+      <c r="Z3">
+        <v>0.02528735632183908</v>
+      </c>
+      <c r="AA3">
+        <v>-0.02426564495530013</v>
       </c>
       <c r="AB3">
-        <v>0.1321216993065164</v>
+        <v>0.1125208223694313</v>
+      </c>
+      <c r="AC3">
+        <v>-0.1367864673247314</v>
       </c>
       <c r="AD3">
-        <v>0.015</v>
+        <v>0.097</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.015</v>
+        <v>0.097</v>
       </c>
       <c r="AG3">
-        <v>0.009999999999999998</v>
+        <v>0.021</v>
       </c>
       <c r="AH3">
-        <v>0.009646302250803859</v>
+        <v>0.02872371927746521</v>
       </c>
       <c r="AI3">
-        <v>2.142857142857143</v>
+        <v>0.02137976636543971</v>
       </c>
       <c r="AJ3">
-        <v>0.006451612903225806</v>
+        <v>0.006361708573159651</v>
       </c>
       <c r="AK3">
-        <v>5.000000000000004</v>
+        <v>0.004707464694014796</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>-0.003</v>
+      </c>
+      <c r="AN3">
+        <v>-1.197530864197531</v>
+      </c>
+      <c r="AP3">
+        <v>-0.2592592592592593</v>
+      </c>
+      <c r="AQ3">
+        <v>31.66666666666667</v>
       </c>
     </row>
     <row r="4">
@@ -799,7 +832,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BTC Studios S.A. (WSE:BTC)</t>
+          <t>Planet B2B S.A. (WSE:P2B)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -808,25 +841,25 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.239</v>
+        <v>-0.455</v>
       </c>
       <c r="G4">
-        <v>-1.12807881773399</v>
+        <v>0.124031007751938</v>
       </c>
       <c r="H4">
-        <v>-1.12807881773399</v>
+        <v>0.124031007751938</v>
       </c>
       <c r="I4">
-        <v>-0.2068965517241379</v>
+        <v>-0.1007751937984496</v>
       </c>
       <c r="J4">
-        <v>-0.2068965517241379</v>
+        <v>-0.1007751937984496</v>
       </c>
       <c r="K4">
-        <v>-0.048</v>
+        <v>-0.027</v>
       </c>
       <c r="L4">
-        <v>-0.2364532019704433</v>
+        <v>-0.1046511627906977</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -850,70 +883,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0.15</v>
+        <v>0.074</v>
       </c>
       <c r="V4">
-        <v>0.04854368932038835</v>
+        <v>0.01836228287841191</v>
       </c>
       <c r="W4">
-        <v>-0.01967213114754099</v>
+        <v>-0.2</v>
       </c>
       <c r="X4">
-        <v>0.1337168666767719</v>
+        <v>0.1126405886892277</v>
       </c>
       <c r="Y4">
-        <v>-0.1533889978243129</v>
+        <v>-0.3126405886892277</v>
       </c>
       <c r="Z4">
-        <v>0.08302658486707568</v>
+        <v>2.031496062992126</v>
       </c>
       <c r="AA4">
-        <v>-0.01717791411042945</v>
+        <v>-0.2047244094488189</v>
       </c>
       <c r="AB4">
-        <v>0.1321160326128718</v>
+        <v>0.1126405886892277</v>
       </c>
       <c r="AC4">
-        <v>-0.1492939467233013</v>
+        <v>-0.3173649981380466</v>
       </c>
       <c r="AD4">
-        <v>0.065</v>
+        <v>0</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.065</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>-0.08499999999999999</v>
+        <v>-0.074</v>
       </c>
       <c r="AH4">
-        <v>0.02060221870047544</v>
+        <v>0</v>
       </c>
       <c r="AI4">
-        <v>0.01599015990159901</v>
+        <v>0</v>
       </c>
       <c r="AJ4">
-        <v>-0.02828618968386023</v>
+        <v>-0.01870576339737108</v>
       </c>
       <c r="AK4">
-        <v>-0.02171136653895274</v>
+        <v>-1.85</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="AM4">
-        <v>-0.062</v>
+        <v>0.005</v>
       </c>
       <c r="AN4">
-        <v>-1.181818181818182</v>
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>-5.199999999999999</v>
       </c>
       <c r="AP4">
-        <v>1.545454545454545</v>
+        <v>-74</v>
       </c>
       <c r="AQ4">
-        <v>0.6774193548387097</v>
+        <v>-5.199999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -924,7 +960,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Planet B2B S.A. (WSE:P2B)</t>
+          <t>Foothills S.A. (WSE:FTL)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -933,25 +969,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.418</v>
-      </c>
-      <c r="G5">
-        <v>0.7192118226600984</v>
-      </c>
-      <c r="H5">
-        <v>0.7192118226600984</v>
-      </c>
-      <c r="I5">
-        <v>-0.02463054187192118</v>
-      </c>
-      <c r="J5">
-        <v>-0.02463054187192118</v>
+        <v>-0.7340000000000001</v>
       </c>
       <c r="K5">
-        <v>-0.006</v>
-      </c>
-      <c r="L5">
-        <v>-0.02955665024630542</v>
+        <v>-0.029</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -975,55 +996,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>0.008</v>
+        <v>0</v>
       </c>
       <c r="V5">
-        <v>0.001317957166392092</v>
+        <v>0</v>
       </c>
       <c r="W5">
-        <v>-0.0340909090909091</v>
+        <v>3.625</v>
       </c>
       <c r="X5">
-        <v>0.1321266886325951</v>
+        <v>0.1151098450724592</v>
       </c>
       <c r="Y5">
-        <v>-0.1662175977235042</v>
+        <v>3.509890154927541</v>
       </c>
       <c r="Z5">
-        <v>1.237804878048781</v>
+        <v>0</v>
       </c>
       <c r="AA5">
-        <v>-0.03048780487804878</v>
+        <v>-14.00000000000001</v>
       </c>
       <c r="AB5">
-        <v>0.1321266886325951</v>
+        <v>0.1125609879903961</v>
       </c>
       <c r="AC5">
-        <v>-0.1626144935106439</v>
+        <v>-14.1125609879904</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>0.045</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>0.045</v>
       </c>
       <c r="AG5">
-        <v>-0.008</v>
+        <v>0.045</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>0.03964757709251101</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>7.500000000000002</v>
       </c>
       <c r="AJ5">
-        <v>-0.001319696469811943</v>
+        <v>0.03964757709251101</v>
       </c>
       <c r="AK5">
-        <v>-0.06299212598425197</v>
+        <v>7.500000000000002</v>
       </c>
       <c r="AL5">
         <v>0.001</v>
@@ -1032,10 +1053,10 @@
         <v>0.001</v>
       </c>
       <c r="AO5">
-        <v>-5</v>
+        <v>-28</v>
       </c>
       <c r="AQ5">
-        <v>-5</v>
+        <v>-28</v>
       </c>
     </row>
   </sheetData>
